--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
